--- a/priorshift/ABTC_priorshift_summary.xlsx
+++ b/priorshift/ABTC_priorshift_summary.xlsx
@@ -3635,7 +3635,6 @@
       <c r="I2" t="n">
         <v>0.2449072066592693</v>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>3.27532884950596e-28</v>
       </c>
@@ -3675,7 +3674,6 @@
       <c r="I3" t="n">
         <v>0.2381526410608527</v>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
         <v>9.663983378991769e-27</v>
       </c>
@@ -3715,7 +3713,6 @@
       <c r="I4" t="n">
         <v>0.2690750857638884</v>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>1.696493370366811e-28</v>
       </c>
@@ -3755,7 +3752,6 @@
       <c r="I5" t="n">
         <v>0.1419849482856557</v>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>7.891047757676894e-19</v>
       </c>
@@ -3795,7 +3791,6 @@
       <c r="I6" t="n">
         <v>0.2514906474325036</v>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
         <v>2.047673963905909e-22</v>
       </c>
@@ -3835,7 +3830,6 @@
       <c r="I7" t="n">
         <v>0.2502080055191243</v>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>1.919675719807487e-22</v>
       </c>
@@ -3875,7 +3869,6 @@
       <c r="I8" t="n">
         <v>0.2687806964527094</v>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
         <v>9.59110716635608e-27</v>
       </c>
@@ -3915,7 +3908,6 @@
       <c r="I9" t="n">
         <v>0.2128300558503097</v>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
         <v>2.380368349007009e-17</v>
       </c>
@@ -3955,7 +3947,6 @@
       <c r="I10" t="n">
         <v>0.263741383327608</v>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
         <v>0.3100355333451216</v>
       </c>
@@ -3995,7 +3986,6 @@
       <c r="I11" t="n">
         <v>0.275124471661545</v>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
         <v>2.018094603687443e-10</v>
       </c>
@@ -4035,7 +4025,6 @@
       <c r="I12" t="n">
         <v>0.267468861966163</v>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>5.043650112258668e-07</v>
       </c>
@@ -4075,7 +4064,6 @@
       <c r="I13" t="n">
         <v>0.2745252011627097</v>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
         <v>1.179821883901599e-10</v>
       </c>
@@ -4115,7 +4103,6 @@
       <c r="I14" t="n">
         <v>0.3014724759968295</v>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
         <v>1.190509590633568e-18</v>
       </c>
@@ -4155,7 +4142,6 @@
       <c r="I15" t="n">
         <v>0.3365788020574298</v>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
         <v>3.737750170328099e-26</v>
       </c>
@@ -4195,7 +4181,6 @@
       <c r="I16" t="n">
         <v>0.2771329510738462</v>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
         <v>1.65823276309948e-12</v>
       </c>
@@ -4235,7 +4220,6 @@
       <c r="I17" t="n">
         <v>0.2696758522972048</v>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
         <v>8.402488842326165e-12</v>
       </c>
@@ -4275,7 +4259,6 @@
       <c r="I18" t="n">
         <v>0.3909024816327922</v>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
         <v>4.681126767463039e-26</v>
       </c>
@@ -4315,7 +4298,6 @@
       <c r="I19" t="n">
         <v>0.4424303790627833</v>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
         <v>4.55528787269114e-29</v>
       </c>
@@ -4355,7 +4337,6 @@
       <c r="I20" t="n">
         <v>0.3188522280115971</v>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
         <v>2.74476790283044e-24</v>
       </c>
@@ -4395,7 +4376,6 @@
       <c r="I21" t="n">
         <v>0.1721386338775379</v>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
         <v>8.103574098789362e-20</v>
       </c>
@@ -29657,7 +29637,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Re-tuned on labelled shifted data (reference)</t>
+          <t>Re-tuned on source validation data resampled to the known prior</t>
         </is>
       </c>
     </row>
